--- a/基本設計/17_日報通知ログ_DB基本設計書.xlsx
+++ b/基本設計/17_日報通知ログ_DB基本設計書.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R61eaf72165714ff1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rb6e836dcf40e4e38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_テーブル一覧" sheetId="23" r:id="R9b7e26cd824c411c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_ER関係" sheetId="24" r:id="R1a7b8841bf19408e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_論理項目定義" sheetId="25" r:id="R26eb4a615f214883"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_制約・索引" sheetId="26" r:id="R90032f8b58d44549"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_ステータス定義" sheetId="27" r:id="Rfa4a43ad03a14fb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rfebdbc6e76064f32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R0f5ee53e89684ed4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_テーブル一覧" sheetId="23" r:id="Rdc3088886e704c16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_ER関係" sheetId="24" r:id="R86ed106f6f714f06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_論理項目定義" sheetId="25" r:id="R5457770e69e84ab4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_制約・索引" sheetId="26" r:id="Ra54359d340ed43b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_ステータス定義" sheetId="27" r:id="Rdc25e08c0f5c4458"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1179,10 +1179,7 @@
       <x:c r="F16" s="167"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1198,25 +1195,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="210" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="210"/>
-      <x:c r="D19" s="210"/>
-      <x:c r="E19" s="210"/>
-      <x:c r="F19" s="210"/>
-      <x:c r="G19" s="210"/>
-      <x:c r="H19" s="210"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="210"/>
-      <x:c r="C20" s="210"/>
-      <x:c r="D20" s="210"/>
-      <x:c r="E20" s="210"/>
-      <x:c r="F20" s="210"/>
-      <x:c r="G20" s="210"/>
-      <x:c r="H20" s="210"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="210"/>
